--- a/Income_Forecast.xlsx
+++ b/Income_Forecast.xlsx
@@ -13,7 +13,9 @@
     <sheet name="Month-End Provisions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forecast Log'!$A$4:$Q$64</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -28,7 +30,7 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="£#,##0;(£#,##0);-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +82,12 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -136,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +177,14 @@
     <xf numFmtId="169" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -176,13 +192,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +457,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="2880000"/>
@@ -767,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -879,29 +908,50 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="17" ht="45" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>e.  Record the reforecast on the FLAGGED month's row: set Variance Status (Reforecast = you re-based it next month; Accepted = variance accepted, no reforecast needed), plus Reforecast By and Reforecast Date. This is the audit trail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Tracking reforecasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>The Forecast Log's right-hand columns show whether each flagged variance has been actioned. Reforecast Entered? auto-detects whether a later month's row exists for that engagement. Outstanding? shows YES (red) for any variance not yet signed off, and Action Note tells you what's needed ('Awaiting reforecast', 'Reforecast entered — confirm sign-off', or 'Signed off'). Use the header AutoFilter to filter Outstanding? = YES, or filter by Engagement Manager. The Dashboard's Open Variances panel counts outstanding items overall, per engagement and per EM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Colour key</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Blue text on pale-yellow fill = cells you fill in.   Black text = calculated, do not edit.   Green text = pulled from another tab.   Red / amber fills = under / over variance flags.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="23" ht="45" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>· % complete is stored as a fraction (enter 25% or 0.25, not 25).   · All amounts are GBP.   · Dates are the first of the month (e.g. 01-Sep-2026 shows as Sep-2026).   · The three demo engagements (M-1001/1002/1003) are examples — delete them once you add your own.</t>
         </is>
@@ -1287,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1300,6 +1350,13 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1367,6 +1424,41 @@
           <t>Remaining Fee (£)</t>
         </is>
       </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>Engagement Manager</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>Variance Status</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>Reforecast By</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Reforecast Date</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Reforecast Entered?</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>Outstanding?</t>
+        </is>
+      </c>
+      <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>Action Note</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1408,6 +1500,25 @@
         <f>IF($A5="","",$C5-$I5)</f>
         <v>108000</v>
       </c>
+      <c r="K5" s="18" t="str">
+        <f>IF($A5="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A5,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v>Priya Shah</v>
+      </c>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="19" t="str">
+        <f>IF(OR($H5="",$H5=0),"",IF(COUNTIFS($A$5:$A$64,$A5,$B$5:$B$64,"&gt;"&amp;$B5)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P5" s="20" t="str">
+        <f>IF(AND($H5&lt;&gt;"",$H5&lt;&gt;0,NOT(OR($L5="Reforecast",$L5="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="21" t="str">
+        <f>IF(OR($H5="",$H5=0),"",IF(OR($L5="Reforecast",$L5="Accepted"),"Signed off: "&amp;$L5,IF($O5="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1449,6 +1560,25 @@
         <f>IF($A6="","",$C6-$I6)</f>
         <v>93000</v>
       </c>
+      <c r="K6" s="18" t="str">
+        <f>IF($A6="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A6,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v>Priya Shah</v>
+      </c>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="19" t="str">
+        <f>IF(OR($H6="",$H6=0),"",IF(COUNTIFS($A$5:$A$64,$A6,$B$5:$B$64,"&gt;"&amp;$B6)&gt;0,"Yes","No"))</f>
+        <v>Yes</v>
+      </c>
+      <c r="P6" s="20" t="str">
+        <f>IF(AND($H6&lt;&gt;"",$H6&lt;&gt;0,NOT(OR($L6="Reforecast",$L6="Accepted"))),"YES","")</f>
+        <v>YES</v>
+      </c>
+      <c r="Q6" s="21" t="str">
+        <f>IF(OR($H6="",$H6=0),"",IF(OR($L6="Reforecast",$L6="Accepted"),"Signed off: "&amp;$L6,IF($O6="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v>Reforecast entered — confirm sign-off</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1490,6 +1620,25 @@
         <f>IF($A7="","",$C7-$I7)</f>
         <v>67000</v>
       </c>
+      <c r="K7" s="18" t="str">
+        <f>IF($A7="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A7,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v>Priya Shah</v>
+      </c>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="19" t="str">
+        <f>IF(OR($H7="",$H7=0),"",IF(COUNTIFS($A$5:$A$64,$A7,$B$5:$B$64,"&gt;"&amp;$B7)&gt;0,"Yes","No"))</f>
+        <v>No</v>
+      </c>
+      <c r="P7" s="20" t="str">
+        <f>IF(AND($H7&lt;&gt;"",$H7&lt;&gt;0,NOT(OR($L7="Reforecast",$L7="Accepted"))),"YES","")</f>
+        <v>YES</v>
+      </c>
+      <c r="Q7" s="21" t="str">
+        <f>IF(OR($H7="",$H7=0),"",IF(OR($L7="Reforecast",$L7="Accepted"),"Signed off: "&amp;$L7,IF($O7="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v>Awaiting reforecast</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1531,6 +1680,25 @@
         <f>IF($A8="","",$C8-$I8)</f>
         <v>76500</v>
       </c>
+      <c r="K8" s="18" t="str">
+        <f>IF($A8="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A8,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v>James Okoro</v>
+      </c>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="19" t="str">
+        <f>IF(OR($H8="",$H8=0),"",IF(COUNTIFS($A$5:$A$64,$A8,$B$5:$B$64,"&gt;"&amp;$B8)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P8" s="20" t="str">
+        <f>IF(AND($H8&lt;&gt;"",$H8&lt;&gt;0,NOT(OR($L8="Reforecast",$L8="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="21" t="str">
+        <f>IF(OR($H8="",$H8=0),"",IF(OR($L8="Reforecast",$L8="Accepted"),"Signed off: "&amp;$L8,IF($O8="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1572,6 +1740,25 @@
         <f>IF($A9="","",$C9-$I9)</f>
         <v>76500</v>
       </c>
+      <c r="K9" s="18" t="str">
+        <f>IF($A9="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A9,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v>James Okoro</v>
+      </c>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="19" t="str">
+        <f>IF(OR($H9="",$H9=0),"",IF(COUNTIFS($A$5:$A$64,$A9,$B$5:$B$64,"&gt;"&amp;$B9)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P9" s="20" t="str">
+        <f>IF(AND($H9&lt;&gt;"",$H9&lt;&gt;0,NOT(OR($L9="Reforecast",$L9="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q9" s="21" t="str">
+        <f>IF(OR($H9="",$H9=0),"",IF(OR($L9="Reforecast",$L9="Accepted"),"Signed off: "&amp;$L9,IF($O9="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1613,6 +1800,25 @@
         <f>IF($A10="","",$C10-$I10)</f>
         <v>48000</v>
       </c>
+      <c r="K10" s="18" t="str">
+        <f>IF($A10="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A10,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v>Priya Shah</v>
+      </c>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="9" t="n"/>
+      <c r="O10" s="19" t="str">
+        <f>IF(OR($H10="",$H10=0),"",IF(COUNTIFS($A$5:$A$64,$A10,$B$5:$B$64,"&gt;"&amp;$B10)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P10" s="20" t="str">
+        <f>IF(AND($H10&lt;&gt;"",$H10&lt;&gt;0,NOT(OR($L10="Reforecast",$L10="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="21" t="str">
+        <f>IF(OR($H10="",$H10=0),"",IF(OR($L10="Reforecast",$L10="Accepted"),"Signed off: "&amp;$L10,IF($O10="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1654,6 +1860,35 @@
         <f>IF($A11="","",$C11-$I11)</f>
         <v>37000</v>
       </c>
+      <c r="K11" s="18" t="str">
+        <f>IF($A11="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A11,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v>Priya Shah</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Reforecast</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>46330</v>
+      </c>
+      <c r="O11" s="19" t="str">
+        <f>IF(OR($H11="",$H11=0),"",IF(COUNTIFS($A$5:$A$64,$A11,$B$5:$B$64,"&gt;"&amp;$B11)&gt;0,"Yes","No"))</f>
+        <v>Yes</v>
+      </c>
+      <c r="P11" s="20" t="str">
+        <f>IF(AND($H11&lt;&gt;"",$H11&lt;&gt;0,NOT(OR($L11="Reforecast",$L11="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="21" t="str">
+        <f>IF(OR($H11="",$H11=0),"",IF(OR($L11="Reforecast",$L11="Accepted"),"Signed off: "&amp;$L11,IF($O11="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v>Signed off: Reforecast</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1694,6 +1929,25 @@
       <c r="J12" s="15">
         <f>IF($A12="","",$C12-$I12)</f>
         <v>37000</v>
+      </c>
+      <c r="K12" s="18" t="str">
+        <f>IF($A12="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A12,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v>Priya Shah</v>
+      </c>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="9" t="n"/>
+      <c r="O12" s="19" t="str">
+        <f>IF(OR($H12="",$H12=0),"",IF(COUNTIFS($A$5:$A$64,$A12,$B$5:$B$64,"&gt;"&amp;$B12)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P12" s="20" t="str">
+        <f>IF(AND($H12&lt;&gt;"",$H12&lt;&gt;0,NOT(OR($L12="Reforecast",$L12="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="21" t="str">
+        <f>IF(OR($H12="",$H12=0),"",IF(OR($L12="Reforecast",$L12="Accepted"),"Signed off: "&amp;$L12,IF($O12="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1728,6 +1982,25 @@
         <f>IF($A13="","",$C13-$I13)</f>
         <v/>
       </c>
+      <c r="K13" s="18" t="str">
+        <f>IF($A13="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A13,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="9" t="n"/>
+      <c r="O13" s="19" t="str">
+        <f>IF(OR($H13="",$H13=0),"",IF(COUNTIFS($A$5:$A$64,$A13,$B$5:$B$64,"&gt;"&amp;$B13)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P13" s="20" t="str">
+        <f>IF(AND($H13&lt;&gt;"",$H13&lt;&gt;0,NOT(OR($L13="Reforecast",$L13="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="21" t="str">
+        <f>IF(OR($H13="",$H13=0),"",IF(OR($L13="Reforecast",$L13="Accepted"),"Signed off: "&amp;$L13,IF($O13="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -1761,6 +2034,25 @@
         <f>IF($A14="","",$C14-$I14)</f>
         <v/>
       </c>
+      <c r="K14" s="18" t="str">
+        <f>IF($A14="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A14,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="19" t="str">
+        <f>IF(OR($H14="",$H14=0),"",IF(COUNTIFS($A$5:$A$64,$A14,$B$5:$B$64,"&gt;"&amp;$B14)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P14" s="20" t="str">
+        <f>IF(AND($H14&lt;&gt;"",$H14&lt;&gt;0,NOT(OR($L14="Reforecast",$L14="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="21" t="str">
+        <f>IF(OR($H14="",$H14=0),"",IF(OR($L14="Reforecast",$L14="Accepted"),"Signed off: "&amp;$L14,IF($O14="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -1794,6 +2086,25 @@
         <f>IF($A15="","",$C15-$I15)</f>
         <v/>
       </c>
+      <c r="K15" s="18" t="str">
+        <f>IF($A15="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A15,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="19" t="str">
+        <f>IF(OR($H15="",$H15=0),"",IF(COUNTIFS($A$5:$A$64,$A15,$B$5:$B$64,"&gt;"&amp;$B15)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P15" s="20" t="str">
+        <f>IF(AND($H15&lt;&gt;"",$H15&lt;&gt;0,NOT(OR($L15="Reforecast",$L15="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="21" t="str">
+        <f>IF(OR($H15="",$H15=0),"",IF(OR($L15="Reforecast",$L15="Accepted"),"Signed off: "&amp;$L15,IF($O15="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -1827,6 +2138,25 @@
         <f>IF($A16="","",$C16-$I16)</f>
         <v/>
       </c>
+      <c r="K16" s="18" t="str">
+        <f>IF($A16="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A16,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="19" t="str">
+        <f>IF(OR($H16="",$H16=0),"",IF(COUNTIFS($A$5:$A$64,$A16,$B$5:$B$64,"&gt;"&amp;$B16)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P16" s="20" t="str">
+        <f>IF(AND($H16&lt;&gt;"",$H16&lt;&gt;0,NOT(OR($L16="Reforecast",$L16="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="21" t="str">
+        <f>IF(OR($H16="",$H16=0),"",IF(OR($L16="Reforecast",$L16="Accepted"),"Signed off: "&amp;$L16,IF($O16="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -1860,6 +2190,25 @@
         <f>IF($A17="","",$C17-$I17)</f>
         <v/>
       </c>
+      <c r="K17" s="18" t="str">
+        <f>IF($A17="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A17,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="19" t="str">
+        <f>IF(OR($H17="",$H17=0),"",IF(COUNTIFS($A$5:$A$64,$A17,$B$5:$B$64,"&gt;"&amp;$B17)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P17" s="20" t="str">
+        <f>IF(AND($H17&lt;&gt;"",$H17&lt;&gt;0,NOT(OR($L17="Reforecast",$L17="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="21" t="str">
+        <f>IF(OR($H17="",$H17=0),"",IF(OR($L17="Reforecast",$L17="Accepted"),"Signed off: "&amp;$L17,IF($O17="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -1893,6 +2242,25 @@
         <f>IF($A18="","",$C18-$I18)</f>
         <v/>
       </c>
+      <c r="K18" s="18" t="str">
+        <f>IF($A18="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A18,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="19" t="str">
+        <f>IF(OR($H18="",$H18=0),"",IF(COUNTIFS($A$5:$A$64,$A18,$B$5:$B$64,"&gt;"&amp;$B18)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P18" s="20" t="str">
+        <f>IF(AND($H18&lt;&gt;"",$H18&lt;&gt;0,NOT(OR($L18="Reforecast",$L18="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="21" t="str">
+        <f>IF(OR($H18="",$H18=0),"",IF(OR($L18="Reforecast",$L18="Accepted"),"Signed off: "&amp;$L18,IF($O18="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -1926,6 +2294,25 @@
         <f>IF($A19="","",$C19-$I19)</f>
         <v/>
       </c>
+      <c r="K19" s="18" t="str">
+        <f>IF($A19="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A19,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="19" t="str">
+        <f>IF(OR($H19="",$H19=0),"",IF(COUNTIFS($A$5:$A$64,$A19,$B$5:$B$64,"&gt;"&amp;$B19)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P19" s="20" t="str">
+        <f>IF(AND($H19&lt;&gt;"",$H19&lt;&gt;0,NOT(OR($L19="Reforecast",$L19="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="21" t="str">
+        <f>IF(OR($H19="",$H19=0),"",IF(OR($L19="Reforecast",$L19="Accepted"),"Signed off: "&amp;$L19,IF($O19="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1959,6 +2346,25 @@
         <f>IF($A20="","",$C20-$I20)</f>
         <v/>
       </c>
+      <c r="K20" s="18" t="str">
+        <f>IF($A20="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A20,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="19" t="str">
+        <f>IF(OR($H20="",$H20=0),"",IF(COUNTIFS($A$5:$A$64,$A20,$B$5:$B$64,"&gt;"&amp;$B20)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P20" s="20" t="str">
+        <f>IF(AND($H20&lt;&gt;"",$H20&lt;&gt;0,NOT(OR($L20="Reforecast",$L20="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="21" t="str">
+        <f>IF(OR($H20="",$H20=0),"",IF(OR($L20="Reforecast",$L20="Accepted"),"Signed off: "&amp;$L20,IF($O20="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1992,6 +2398,25 @@
         <f>IF($A21="","",$C21-$I21)</f>
         <v/>
       </c>
+      <c r="K21" s="18" t="str">
+        <f>IF($A21="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A21,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="19" t="str">
+        <f>IF(OR($H21="",$H21=0),"",IF(COUNTIFS($A$5:$A$64,$A21,$B$5:$B$64,"&gt;"&amp;$B21)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P21" s="20" t="str">
+        <f>IF(AND($H21&lt;&gt;"",$H21&lt;&gt;0,NOT(OR($L21="Reforecast",$L21="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="21" t="str">
+        <f>IF(OR($H21="",$H21=0),"",IF(OR($L21="Reforecast",$L21="Accepted"),"Signed off: "&amp;$L21,IF($O21="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -2025,6 +2450,25 @@
         <f>IF($A22="","",$C22-$I22)</f>
         <v/>
       </c>
+      <c r="K22" s="18" t="str">
+        <f>IF($A22="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A22,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="19" t="str">
+        <f>IF(OR($H22="",$H22=0),"",IF(COUNTIFS($A$5:$A$64,$A22,$B$5:$B$64,"&gt;"&amp;$B22)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P22" s="20" t="str">
+        <f>IF(AND($H22&lt;&gt;"",$H22&lt;&gt;0,NOT(OR($L22="Reforecast",$L22="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="21" t="str">
+        <f>IF(OR($H22="",$H22=0),"",IF(OR($L22="Reforecast",$L22="Accepted"),"Signed off: "&amp;$L22,IF($O22="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -2058,6 +2502,25 @@
         <f>IF($A23="","",$C23-$I23)</f>
         <v/>
       </c>
+      <c r="K23" s="18" t="str">
+        <f>IF($A23="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A23,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="19" t="str">
+        <f>IF(OR($H23="",$H23=0),"",IF(COUNTIFS($A$5:$A$64,$A23,$B$5:$B$64,"&gt;"&amp;$B23)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P23" s="20" t="str">
+        <f>IF(AND($H23&lt;&gt;"",$H23&lt;&gt;0,NOT(OR($L23="Reforecast",$L23="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="21" t="str">
+        <f>IF(OR($H23="",$H23=0),"",IF(OR($L23="Reforecast",$L23="Accepted"),"Signed off: "&amp;$L23,IF($O23="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -2091,6 +2554,25 @@
         <f>IF($A24="","",$C24-$I24)</f>
         <v/>
       </c>
+      <c r="K24" s="18" t="str">
+        <f>IF($A24="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A24,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="19" t="str">
+        <f>IF(OR($H24="",$H24=0),"",IF(COUNTIFS($A$5:$A$64,$A24,$B$5:$B$64,"&gt;"&amp;$B24)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P24" s="20" t="str">
+        <f>IF(AND($H24&lt;&gt;"",$H24&lt;&gt;0,NOT(OR($L24="Reforecast",$L24="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="21" t="str">
+        <f>IF(OR($H24="",$H24=0),"",IF(OR($L24="Reforecast",$L24="Accepted"),"Signed off: "&amp;$L24,IF($O24="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -2124,6 +2606,25 @@
         <f>IF($A25="","",$C25-$I25)</f>
         <v/>
       </c>
+      <c r="K25" s="18" t="str">
+        <f>IF($A25="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A25,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="19" t="str">
+        <f>IF(OR($H25="",$H25=0),"",IF(COUNTIFS($A$5:$A$64,$A25,$B$5:$B$64,"&gt;"&amp;$B25)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P25" s="20" t="str">
+        <f>IF(AND($H25&lt;&gt;"",$H25&lt;&gt;0,NOT(OR($L25="Reforecast",$L25="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="21" t="str">
+        <f>IF(OR($H25="",$H25=0),"",IF(OR($L25="Reforecast",$L25="Accepted"),"Signed off: "&amp;$L25,IF($O25="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -2157,6 +2658,25 @@
         <f>IF($A26="","",$C26-$I26)</f>
         <v/>
       </c>
+      <c r="K26" s="18" t="str">
+        <f>IF($A26="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A26,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="19" t="str">
+        <f>IF(OR($H26="",$H26=0),"",IF(COUNTIFS($A$5:$A$64,$A26,$B$5:$B$64,"&gt;"&amp;$B26)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P26" s="20" t="str">
+        <f>IF(AND($H26&lt;&gt;"",$H26&lt;&gt;0,NOT(OR($L26="Reforecast",$L26="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="21" t="str">
+        <f>IF(OR($H26="",$H26=0),"",IF(OR($L26="Reforecast",$L26="Accepted"),"Signed off: "&amp;$L26,IF($O26="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -2190,6 +2710,25 @@
         <f>IF($A27="","",$C27-$I27)</f>
         <v/>
       </c>
+      <c r="K27" s="18" t="str">
+        <f>IF($A27="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A27,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="19" t="str">
+        <f>IF(OR($H27="",$H27=0),"",IF(COUNTIFS($A$5:$A$64,$A27,$B$5:$B$64,"&gt;"&amp;$B27)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P27" s="20" t="str">
+        <f>IF(AND($H27&lt;&gt;"",$H27&lt;&gt;0,NOT(OR($L27="Reforecast",$L27="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="21" t="str">
+        <f>IF(OR($H27="",$H27=0),"",IF(OR($L27="Reforecast",$L27="Accepted"),"Signed off: "&amp;$L27,IF($O27="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -2223,6 +2762,25 @@
         <f>IF($A28="","",$C28-$I28)</f>
         <v/>
       </c>
+      <c r="K28" s="18" t="str">
+        <f>IF($A28="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A28,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="9" t="n"/>
+      <c r="O28" s="19" t="str">
+        <f>IF(OR($H28="",$H28=0),"",IF(COUNTIFS($A$5:$A$64,$A28,$B$5:$B$64,"&gt;"&amp;$B28)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P28" s="20" t="str">
+        <f>IF(AND($H28&lt;&gt;"",$H28&lt;&gt;0,NOT(OR($L28="Reforecast",$L28="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="21" t="str">
+        <f>IF(OR($H28="",$H28=0),"",IF(OR($L28="Reforecast",$L28="Accepted"),"Signed off: "&amp;$L28,IF($O28="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -2256,6 +2814,25 @@
         <f>IF($A29="","",$C29-$I29)</f>
         <v/>
       </c>
+      <c r="K29" s="18" t="str">
+        <f>IF($A29="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A29,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="19" t="str">
+        <f>IF(OR($H29="",$H29=0),"",IF(COUNTIFS($A$5:$A$64,$A29,$B$5:$B$64,"&gt;"&amp;$B29)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P29" s="20" t="str">
+        <f>IF(AND($H29&lt;&gt;"",$H29&lt;&gt;0,NOT(OR($L29="Reforecast",$L29="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="21" t="str">
+        <f>IF(OR($H29="",$H29=0),"",IF(OR($L29="Reforecast",$L29="Accepted"),"Signed off: "&amp;$L29,IF($O29="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -2289,6 +2866,25 @@
         <f>IF($A30="","",$C30-$I30)</f>
         <v/>
       </c>
+      <c r="K30" s="18" t="str">
+        <f>IF($A30="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A30,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="19" t="str">
+        <f>IF(OR($H30="",$H30=0),"",IF(COUNTIFS($A$5:$A$64,$A30,$B$5:$B$64,"&gt;"&amp;$B30)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P30" s="20" t="str">
+        <f>IF(AND($H30&lt;&gt;"",$H30&lt;&gt;0,NOT(OR($L30="Reforecast",$L30="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q30" s="21" t="str">
+        <f>IF(OR($H30="",$H30=0),"",IF(OR($L30="Reforecast",$L30="Accepted"),"Signed off: "&amp;$L30,IF($O30="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -2322,6 +2918,25 @@
         <f>IF($A31="","",$C31-$I31)</f>
         <v/>
       </c>
+      <c r="K31" s="18" t="str">
+        <f>IF($A31="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A31,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="9" t="n"/>
+      <c r="O31" s="19" t="str">
+        <f>IF(OR($H31="",$H31=0),"",IF(COUNTIFS($A$5:$A$64,$A31,$B$5:$B$64,"&gt;"&amp;$B31)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P31" s="20" t="str">
+        <f>IF(AND($H31&lt;&gt;"",$H31&lt;&gt;0,NOT(OR($L31="Reforecast",$L31="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q31" s="21" t="str">
+        <f>IF(OR($H31="",$H31=0),"",IF(OR($L31="Reforecast",$L31="Accepted"),"Signed off: "&amp;$L31,IF($O31="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -2355,6 +2970,25 @@
         <f>IF($A32="","",$C32-$I32)</f>
         <v/>
       </c>
+      <c r="K32" s="18" t="str">
+        <f>IF($A32="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A32,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="19" t="str">
+        <f>IF(OR($H32="",$H32=0),"",IF(COUNTIFS($A$5:$A$64,$A32,$B$5:$B$64,"&gt;"&amp;$B32)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P32" s="20" t="str">
+        <f>IF(AND($H32&lt;&gt;"",$H32&lt;&gt;0,NOT(OR($L32="Reforecast",$L32="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q32" s="21" t="str">
+        <f>IF(OR($H32="",$H32=0),"",IF(OR($L32="Reforecast",$L32="Accepted"),"Signed off: "&amp;$L32,IF($O32="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -2388,6 +3022,25 @@
         <f>IF($A33="","",$C33-$I33)</f>
         <v/>
       </c>
+      <c r="K33" s="18" t="str">
+        <f>IF($A33="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A33,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="19" t="str">
+        <f>IF(OR($H33="",$H33=0),"",IF(COUNTIFS($A$5:$A$64,$A33,$B$5:$B$64,"&gt;"&amp;$B33)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P33" s="20" t="str">
+        <f>IF(AND($H33&lt;&gt;"",$H33&lt;&gt;0,NOT(OR($L33="Reforecast",$L33="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q33" s="21" t="str">
+        <f>IF(OR($H33="",$H33=0),"",IF(OR($L33="Reforecast",$L33="Accepted"),"Signed off: "&amp;$L33,IF($O33="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -2421,6 +3074,25 @@
         <f>IF($A34="","",$C34-$I34)</f>
         <v/>
       </c>
+      <c r="K34" s="18" t="str">
+        <f>IF($A34="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A34,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="19" t="str">
+        <f>IF(OR($H34="",$H34=0),"",IF(COUNTIFS($A$5:$A$64,$A34,$B$5:$B$64,"&gt;"&amp;$B34)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P34" s="20" t="str">
+        <f>IF(AND($H34&lt;&gt;"",$H34&lt;&gt;0,NOT(OR($L34="Reforecast",$L34="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="21" t="str">
+        <f>IF(OR($H34="",$H34=0),"",IF(OR($L34="Reforecast",$L34="Accepted"),"Signed off: "&amp;$L34,IF($O34="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -2454,6 +3126,25 @@
         <f>IF($A35="","",$C35-$I35)</f>
         <v/>
       </c>
+      <c r="K35" s="18" t="str">
+        <f>IF($A35="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A35,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="19" t="str">
+        <f>IF(OR($H35="",$H35=0),"",IF(COUNTIFS($A$5:$A$64,$A35,$B$5:$B$64,"&gt;"&amp;$B35)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P35" s="20" t="str">
+        <f>IF(AND($H35&lt;&gt;"",$H35&lt;&gt;0,NOT(OR($L35="Reforecast",$L35="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="21" t="str">
+        <f>IF(OR($H35="",$H35=0),"",IF(OR($L35="Reforecast",$L35="Accepted"),"Signed off: "&amp;$L35,IF($O35="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -2487,6 +3178,25 @@
         <f>IF($A36="","",$C36-$I36)</f>
         <v/>
       </c>
+      <c r="K36" s="18" t="str">
+        <f>IF($A36="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A36,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="19" t="str">
+        <f>IF(OR($H36="",$H36=0),"",IF(COUNTIFS($A$5:$A$64,$A36,$B$5:$B$64,"&gt;"&amp;$B36)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P36" s="20" t="str">
+        <f>IF(AND($H36&lt;&gt;"",$H36&lt;&gt;0,NOT(OR($L36="Reforecast",$L36="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="21" t="str">
+        <f>IF(OR($H36="",$H36=0),"",IF(OR($L36="Reforecast",$L36="Accepted"),"Signed off: "&amp;$L36,IF($O36="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -2520,6 +3230,25 @@
         <f>IF($A37="","",$C37-$I37)</f>
         <v/>
       </c>
+      <c r="K37" s="18" t="str">
+        <f>IF($A37="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A37,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="19" t="str">
+        <f>IF(OR($H37="",$H37=0),"",IF(COUNTIFS($A$5:$A$64,$A37,$B$5:$B$64,"&gt;"&amp;$B37)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P37" s="20" t="str">
+        <f>IF(AND($H37&lt;&gt;"",$H37&lt;&gt;0,NOT(OR($L37="Reforecast",$L37="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="21" t="str">
+        <f>IF(OR($H37="",$H37=0),"",IF(OR($L37="Reforecast",$L37="Accepted"),"Signed off: "&amp;$L37,IF($O37="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -2553,6 +3282,25 @@
         <f>IF($A38="","",$C38-$I38)</f>
         <v/>
       </c>
+      <c r="K38" s="18" t="str">
+        <f>IF($A38="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A38,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="19" t="str">
+        <f>IF(OR($H38="",$H38=0),"",IF(COUNTIFS($A$5:$A$64,$A38,$B$5:$B$64,"&gt;"&amp;$B38)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P38" s="20" t="str">
+        <f>IF(AND($H38&lt;&gt;"",$H38&lt;&gt;0,NOT(OR($L38="Reforecast",$L38="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="21" t="str">
+        <f>IF(OR($H38="",$H38=0),"",IF(OR($L38="Reforecast",$L38="Accepted"),"Signed off: "&amp;$L38,IF($O38="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -2586,6 +3334,25 @@
         <f>IF($A39="","",$C39-$I39)</f>
         <v/>
       </c>
+      <c r="K39" s="18" t="str">
+        <f>IF($A39="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A39,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="19" t="str">
+        <f>IF(OR($H39="",$H39=0),"",IF(COUNTIFS($A$5:$A$64,$A39,$B$5:$B$64,"&gt;"&amp;$B39)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P39" s="20" t="str">
+        <f>IF(AND($H39&lt;&gt;"",$H39&lt;&gt;0,NOT(OR($L39="Reforecast",$L39="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="21" t="str">
+        <f>IF(OR($H39="",$H39=0),"",IF(OR($L39="Reforecast",$L39="Accepted"),"Signed off: "&amp;$L39,IF($O39="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -2619,6 +3386,25 @@
         <f>IF($A40="","",$C40-$I40)</f>
         <v/>
       </c>
+      <c r="K40" s="18" t="str">
+        <f>IF($A40="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A40,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="19" t="str">
+        <f>IF(OR($H40="",$H40=0),"",IF(COUNTIFS($A$5:$A$64,$A40,$B$5:$B$64,"&gt;"&amp;$B40)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P40" s="20" t="str">
+        <f>IF(AND($H40&lt;&gt;"",$H40&lt;&gt;0,NOT(OR($L40="Reforecast",$L40="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="21" t="str">
+        <f>IF(OR($H40="",$H40=0),"",IF(OR($L40="Reforecast",$L40="Accepted"),"Signed off: "&amp;$L40,IF($O40="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -2652,6 +3438,25 @@
         <f>IF($A41="","",$C41-$I41)</f>
         <v/>
       </c>
+      <c r="K41" s="18" t="str">
+        <f>IF($A41="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A41,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="19" t="str">
+        <f>IF(OR($H41="",$H41=0),"",IF(COUNTIFS($A$5:$A$64,$A41,$B$5:$B$64,"&gt;"&amp;$B41)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P41" s="20" t="str">
+        <f>IF(AND($H41&lt;&gt;"",$H41&lt;&gt;0,NOT(OR($L41="Reforecast",$L41="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q41" s="21" t="str">
+        <f>IF(OR($H41="",$H41=0),"",IF(OR($L41="Reforecast",$L41="Accepted"),"Signed off: "&amp;$L41,IF($O41="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -2685,6 +3490,25 @@
         <f>IF($A42="","",$C42-$I42)</f>
         <v/>
       </c>
+      <c r="K42" s="18" t="str">
+        <f>IF($A42="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A42,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="19" t="str">
+        <f>IF(OR($H42="",$H42=0),"",IF(COUNTIFS($A$5:$A$64,$A42,$B$5:$B$64,"&gt;"&amp;$B42)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P42" s="20" t="str">
+        <f>IF(AND($H42&lt;&gt;"",$H42&lt;&gt;0,NOT(OR($L42="Reforecast",$L42="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q42" s="21" t="str">
+        <f>IF(OR($H42="",$H42=0),"",IF(OR($L42="Reforecast",$L42="Accepted"),"Signed off: "&amp;$L42,IF($O42="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -2718,6 +3542,25 @@
         <f>IF($A43="","",$C43-$I43)</f>
         <v/>
       </c>
+      <c r="K43" s="18" t="str">
+        <f>IF($A43="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A43,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="19" t="str">
+        <f>IF(OR($H43="",$H43=0),"",IF(COUNTIFS($A$5:$A$64,$A43,$B$5:$B$64,"&gt;"&amp;$B43)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P43" s="20" t="str">
+        <f>IF(AND($H43&lt;&gt;"",$H43&lt;&gt;0,NOT(OR($L43="Reforecast",$L43="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q43" s="21" t="str">
+        <f>IF(OR($H43="",$H43=0),"",IF(OR($L43="Reforecast",$L43="Accepted"),"Signed off: "&amp;$L43,IF($O43="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -2751,6 +3594,25 @@
         <f>IF($A44="","",$C44-$I44)</f>
         <v/>
       </c>
+      <c r="K44" s="18" t="str">
+        <f>IF($A44="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A44,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="9" t="n"/>
+      <c r="O44" s="19" t="str">
+        <f>IF(OR($H44="",$H44=0),"",IF(COUNTIFS($A$5:$A$64,$A44,$B$5:$B$64,"&gt;"&amp;$B44)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P44" s="20" t="str">
+        <f>IF(AND($H44&lt;&gt;"",$H44&lt;&gt;0,NOT(OR($L44="Reforecast",$L44="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q44" s="21" t="str">
+        <f>IF(OR($H44="",$H44=0),"",IF(OR($L44="Reforecast",$L44="Accepted"),"Signed off: "&amp;$L44,IF($O44="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -2784,6 +3646,25 @@
         <f>IF($A45="","",$C45-$I45)</f>
         <v/>
       </c>
+      <c r="K45" s="18" t="str">
+        <f>IF($A45="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A45,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="19" t="str">
+        <f>IF(OR($H45="",$H45=0),"",IF(COUNTIFS($A$5:$A$64,$A45,$B$5:$B$64,"&gt;"&amp;$B45)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P45" s="20" t="str">
+        <f>IF(AND($H45&lt;&gt;"",$H45&lt;&gt;0,NOT(OR($L45="Reforecast",$L45="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q45" s="21" t="str">
+        <f>IF(OR($H45="",$H45=0),"",IF(OR($L45="Reforecast",$L45="Accepted"),"Signed off: "&amp;$L45,IF($O45="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -2817,6 +3698,25 @@
         <f>IF($A46="","",$C46-$I46)</f>
         <v/>
       </c>
+      <c r="K46" s="18" t="str">
+        <f>IF($A46="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A46,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="19" t="str">
+        <f>IF(OR($H46="",$H46=0),"",IF(COUNTIFS($A$5:$A$64,$A46,$B$5:$B$64,"&gt;"&amp;$B46)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P46" s="20" t="str">
+        <f>IF(AND($H46&lt;&gt;"",$H46&lt;&gt;0,NOT(OR($L46="Reforecast",$L46="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q46" s="21" t="str">
+        <f>IF(OR($H46="",$H46=0),"",IF(OR($L46="Reforecast",$L46="Accepted"),"Signed off: "&amp;$L46,IF($O46="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -2850,6 +3750,25 @@
         <f>IF($A47="","",$C47-$I47)</f>
         <v/>
       </c>
+      <c r="K47" s="18" t="str">
+        <f>IF($A47="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A47,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L47" s="6" t="n"/>
+      <c r="M47" s="6" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="19" t="str">
+        <f>IF(OR($H47="",$H47=0),"",IF(COUNTIFS($A$5:$A$64,$A47,$B$5:$B$64,"&gt;"&amp;$B47)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P47" s="20" t="str">
+        <f>IF(AND($H47&lt;&gt;"",$H47&lt;&gt;0,NOT(OR($L47="Reforecast",$L47="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q47" s="21" t="str">
+        <f>IF(OR($H47="",$H47=0),"",IF(OR($L47="Reforecast",$L47="Accepted"),"Signed off: "&amp;$L47,IF($O47="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -2883,6 +3802,25 @@
         <f>IF($A48="","",$C48-$I48)</f>
         <v/>
       </c>
+      <c r="K48" s="18" t="str">
+        <f>IF($A48="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A48,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="n"/>
+      <c r="N48" s="9" t="n"/>
+      <c r="O48" s="19" t="str">
+        <f>IF(OR($H48="",$H48=0),"",IF(COUNTIFS($A$5:$A$64,$A48,$B$5:$B$64,"&gt;"&amp;$B48)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P48" s="20" t="str">
+        <f>IF(AND($H48&lt;&gt;"",$H48&lt;&gt;0,NOT(OR($L48="Reforecast",$L48="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q48" s="21" t="str">
+        <f>IF(OR($H48="",$H48=0),"",IF(OR($L48="Reforecast",$L48="Accepted"),"Signed off: "&amp;$L48,IF($O48="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -2916,6 +3854,25 @@
         <f>IF($A49="","",$C49-$I49)</f>
         <v/>
       </c>
+      <c r="K49" s="18" t="str">
+        <f>IF($A49="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A49,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="9" t="n"/>
+      <c r="O49" s="19" t="str">
+        <f>IF(OR($H49="",$H49=0),"",IF(COUNTIFS($A$5:$A$64,$A49,$B$5:$B$64,"&gt;"&amp;$B49)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P49" s="20" t="str">
+        <f>IF(AND($H49&lt;&gt;"",$H49&lt;&gt;0,NOT(OR($L49="Reforecast",$L49="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q49" s="21" t="str">
+        <f>IF(OR($H49="",$H49=0),"",IF(OR($L49="Reforecast",$L49="Accepted"),"Signed off: "&amp;$L49,IF($O49="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -2949,6 +3906,25 @@
         <f>IF($A50="","",$C50-$I50)</f>
         <v/>
       </c>
+      <c r="K50" s="18" t="str">
+        <f>IF($A50="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A50,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
+      <c r="N50" s="9" t="n"/>
+      <c r="O50" s="19" t="str">
+        <f>IF(OR($H50="",$H50=0),"",IF(COUNTIFS($A$5:$A$64,$A50,$B$5:$B$64,"&gt;"&amp;$B50)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P50" s="20" t="str">
+        <f>IF(AND($H50&lt;&gt;"",$H50&lt;&gt;0,NOT(OR($L50="Reforecast",$L50="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q50" s="21" t="str">
+        <f>IF(OR($H50="",$H50=0),"",IF(OR($L50="Reforecast",$L50="Accepted"),"Signed off: "&amp;$L50,IF($O50="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -2982,6 +3958,25 @@
         <f>IF($A51="","",$C51-$I51)</f>
         <v/>
       </c>
+      <c r="K51" s="18" t="str">
+        <f>IF($A51="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A51,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
+      <c r="N51" s="9" t="n"/>
+      <c r="O51" s="19" t="str">
+        <f>IF(OR($H51="",$H51=0),"",IF(COUNTIFS($A$5:$A$64,$A51,$B$5:$B$64,"&gt;"&amp;$B51)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P51" s="20" t="str">
+        <f>IF(AND($H51&lt;&gt;"",$H51&lt;&gt;0,NOT(OR($L51="Reforecast",$L51="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q51" s="21" t="str">
+        <f>IF(OR($H51="",$H51=0),"",IF(OR($L51="Reforecast",$L51="Accepted"),"Signed off: "&amp;$L51,IF($O51="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -3015,6 +4010,25 @@
         <f>IF($A52="","",$C52-$I52)</f>
         <v/>
       </c>
+      <c r="K52" s="18" t="str">
+        <f>IF($A52="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A52,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
+      <c r="N52" s="9" t="n"/>
+      <c r="O52" s="19" t="str">
+        <f>IF(OR($H52="",$H52=0),"",IF(COUNTIFS($A$5:$A$64,$A52,$B$5:$B$64,"&gt;"&amp;$B52)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P52" s="20" t="str">
+        <f>IF(AND($H52&lt;&gt;"",$H52&lt;&gt;0,NOT(OR($L52="Reforecast",$L52="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q52" s="21" t="str">
+        <f>IF(OR($H52="",$H52=0),"",IF(OR($L52="Reforecast",$L52="Accepted"),"Signed off: "&amp;$L52,IF($O52="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -3048,6 +4062,25 @@
         <f>IF($A53="","",$C53-$I53)</f>
         <v/>
       </c>
+      <c r="K53" s="18" t="str">
+        <f>IF($A53="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A53,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="19" t="str">
+        <f>IF(OR($H53="",$H53=0),"",IF(COUNTIFS($A$5:$A$64,$A53,$B$5:$B$64,"&gt;"&amp;$B53)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P53" s="20" t="str">
+        <f>IF(AND($H53&lt;&gt;"",$H53&lt;&gt;0,NOT(OR($L53="Reforecast",$L53="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q53" s="21" t="str">
+        <f>IF(OR($H53="",$H53=0),"",IF(OR($L53="Reforecast",$L53="Accepted"),"Signed off: "&amp;$L53,IF($O53="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -3081,6 +4114,25 @@
         <f>IF($A54="","",$C54-$I54)</f>
         <v/>
       </c>
+      <c r="K54" s="18" t="str">
+        <f>IF($A54="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A54,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L54" s="6" t="n"/>
+      <c r="M54" s="6" t="n"/>
+      <c r="N54" s="9" t="n"/>
+      <c r="O54" s="19" t="str">
+        <f>IF(OR($H54="",$H54=0),"",IF(COUNTIFS($A$5:$A$64,$A54,$B$5:$B$64,"&gt;"&amp;$B54)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P54" s="20" t="str">
+        <f>IF(AND($H54&lt;&gt;"",$H54&lt;&gt;0,NOT(OR($L54="Reforecast",$L54="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q54" s="21" t="str">
+        <f>IF(OR($H54="",$H54=0),"",IF(OR($L54="Reforecast",$L54="Accepted"),"Signed off: "&amp;$L54,IF($O54="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -3114,6 +4166,25 @@
         <f>IF($A55="","",$C55-$I55)</f>
         <v/>
       </c>
+      <c r="K55" s="18" t="str">
+        <f>IF($A55="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A55,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L55" s="6" t="n"/>
+      <c r="M55" s="6" t="n"/>
+      <c r="N55" s="9" t="n"/>
+      <c r="O55" s="19" t="str">
+        <f>IF(OR($H55="",$H55=0),"",IF(COUNTIFS($A$5:$A$64,$A55,$B$5:$B$64,"&gt;"&amp;$B55)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P55" s="20" t="str">
+        <f>IF(AND($H55&lt;&gt;"",$H55&lt;&gt;0,NOT(OR($L55="Reforecast",$L55="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q55" s="21" t="str">
+        <f>IF(OR($H55="",$H55=0),"",IF(OR($L55="Reforecast",$L55="Accepted"),"Signed off: "&amp;$L55,IF($O55="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -3147,6 +4218,25 @@
         <f>IF($A56="","",$C56-$I56)</f>
         <v/>
       </c>
+      <c r="K56" s="18" t="str">
+        <f>IF($A56="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A56,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L56" s="6" t="n"/>
+      <c r="M56" s="6" t="n"/>
+      <c r="N56" s="9" t="n"/>
+      <c r="O56" s="19" t="str">
+        <f>IF(OR($H56="",$H56=0),"",IF(COUNTIFS($A$5:$A$64,$A56,$B$5:$B$64,"&gt;"&amp;$B56)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P56" s="20" t="str">
+        <f>IF(AND($H56&lt;&gt;"",$H56&lt;&gt;0,NOT(OR($L56="Reforecast",$L56="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q56" s="21" t="str">
+        <f>IF(OR($H56="",$H56=0),"",IF(OR($L56="Reforecast",$L56="Accepted"),"Signed off: "&amp;$L56,IF($O56="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -3180,6 +4270,25 @@
         <f>IF($A57="","",$C57-$I57)</f>
         <v/>
       </c>
+      <c r="K57" s="18" t="str">
+        <f>IF($A57="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A57,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L57" s="6" t="n"/>
+      <c r="M57" s="6" t="n"/>
+      <c r="N57" s="9" t="n"/>
+      <c r="O57" s="19" t="str">
+        <f>IF(OR($H57="",$H57=0),"",IF(COUNTIFS($A$5:$A$64,$A57,$B$5:$B$64,"&gt;"&amp;$B57)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P57" s="20" t="str">
+        <f>IF(AND($H57&lt;&gt;"",$H57&lt;&gt;0,NOT(OR($L57="Reforecast",$L57="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q57" s="21" t="str">
+        <f>IF(OR($H57="",$H57=0),"",IF(OR($L57="Reforecast",$L57="Accepted"),"Signed off: "&amp;$L57,IF($O57="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -3213,6 +4322,25 @@
         <f>IF($A58="","",$C58-$I58)</f>
         <v/>
       </c>
+      <c r="K58" s="18" t="str">
+        <f>IF($A58="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A58,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L58" s="6" t="n"/>
+      <c r="M58" s="6" t="n"/>
+      <c r="N58" s="9" t="n"/>
+      <c r="O58" s="19" t="str">
+        <f>IF(OR($H58="",$H58=0),"",IF(COUNTIFS($A$5:$A$64,$A58,$B$5:$B$64,"&gt;"&amp;$B58)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P58" s="20" t="str">
+        <f>IF(AND($H58&lt;&gt;"",$H58&lt;&gt;0,NOT(OR($L58="Reforecast",$L58="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q58" s="21" t="str">
+        <f>IF(OR($H58="",$H58=0),"",IF(OR($L58="Reforecast",$L58="Accepted"),"Signed off: "&amp;$L58,IF($O58="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -3246,6 +4374,25 @@
         <f>IF($A59="","",$C59-$I59)</f>
         <v/>
       </c>
+      <c r="K59" s="18" t="str">
+        <f>IF($A59="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A59,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L59" s="6" t="n"/>
+      <c r="M59" s="6" t="n"/>
+      <c r="N59" s="9" t="n"/>
+      <c r="O59" s="19" t="str">
+        <f>IF(OR($H59="",$H59=0),"",IF(COUNTIFS($A$5:$A$64,$A59,$B$5:$B$64,"&gt;"&amp;$B59)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P59" s="20" t="str">
+        <f>IF(AND($H59&lt;&gt;"",$H59&lt;&gt;0,NOT(OR($L59="Reforecast",$L59="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q59" s="21" t="str">
+        <f>IF(OR($H59="",$H59=0),"",IF(OR($L59="Reforecast",$L59="Accepted"),"Signed off: "&amp;$L59,IF($O59="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -3279,6 +4426,25 @@
         <f>IF($A60="","",$C60-$I60)</f>
         <v/>
       </c>
+      <c r="K60" s="18" t="str">
+        <f>IF($A60="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A60,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L60" s="6" t="n"/>
+      <c r="M60" s="6" t="n"/>
+      <c r="N60" s="9" t="n"/>
+      <c r="O60" s="19" t="str">
+        <f>IF(OR($H60="",$H60=0),"",IF(COUNTIFS($A$5:$A$64,$A60,$B$5:$B$64,"&gt;"&amp;$B60)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P60" s="20" t="str">
+        <f>IF(AND($H60&lt;&gt;"",$H60&lt;&gt;0,NOT(OR($L60="Reforecast",$L60="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q60" s="21" t="str">
+        <f>IF(OR($H60="",$H60=0),"",IF(OR($L60="Reforecast",$L60="Accepted"),"Signed off: "&amp;$L60,IF($O60="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -3312,6 +4478,25 @@
         <f>IF($A61="","",$C61-$I61)</f>
         <v/>
       </c>
+      <c r="K61" s="18" t="str">
+        <f>IF($A61="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A61,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L61" s="6" t="n"/>
+      <c r="M61" s="6" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="19" t="str">
+        <f>IF(OR($H61="",$H61=0),"",IF(COUNTIFS($A$5:$A$64,$A61,$B$5:$B$64,"&gt;"&amp;$B61)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P61" s="20" t="str">
+        <f>IF(AND($H61&lt;&gt;"",$H61&lt;&gt;0,NOT(OR($L61="Reforecast",$L61="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q61" s="21" t="str">
+        <f>IF(OR($H61="",$H61=0),"",IF(OR($L61="Reforecast",$L61="Accepted"),"Signed off: "&amp;$L61,IF($O61="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
@@ -3345,6 +4530,25 @@
         <f>IF($A62="","",$C62-$I62)</f>
         <v/>
       </c>
+      <c r="K62" s="18" t="str">
+        <f>IF($A62="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A62,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L62" s="6" t="n"/>
+      <c r="M62" s="6" t="n"/>
+      <c r="N62" s="9" t="n"/>
+      <c r="O62" s="19" t="str">
+        <f>IF(OR($H62="",$H62=0),"",IF(COUNTIFS($A$5:$A$64,$A62,$B$5:$B$64,"&gt;"&amp;$B62)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P62" s="20" t="str">
+        <f>IF(AND($H62&lt;&gt;"",$H62&lt;&gt;0,NOT(OR($L62="Reforecast",$L62="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q62" s="21" t="str">
+        <f>IF(OR($H62="",$H62=0),"",IF(OR($L62="Reforecast",$L62="Accepted"),"Signed off: "&amp;$L62,IF($O62="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -3378,6 +4582,25 @@
         <f>IF($A63="","",$C63-$I63)</f>
         <v/>
       </c>
+      <c r="K63" s="18" t="str">
+        <f>IF($A63="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A63,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L63" s="6" t="n"/>
+      <c r="M63" s="6" t="n"/>
+      <c r="N63" s="9" t="n"/>
+      <c r="O63" s="19" t="str">
+        <f>IF(OR($H63="",$H63=0),"",IF(COUNTIFS($A$5:$A$64,$A63,$B$5:$B$64,"&gt;"&amp;$B63)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P63" s="20" t="str">
+        <f>IF(AND($H63&lt;&gt;"",$H63&lt;&gt;0,NOT(OR($L63="Reforecast",$L63="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q63" s="21" t="str">
+        <f>IF(OR($H63="",$H63=0),"",IF(OR($L63="Reforecast",$L63="Accepted"),"Signed off: "&amp;$L63,IF($O63="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -3411,8 +4634,28 @@
         <f>IF($A64="","",$C64-$I64)</f>
         <v/>
       </c>
+      <c r="K64" s="18" t="str">
+        <f>IF($A64="","",IFERROR(INDEX('Matters Register'!$D$5:$D$44,MATCH($A64,'Matters Register'!$A$5:$A$44,0)),""))</f>
+        <v/>
+      </c>
+      <c r="L64" s="6" t="n"/>
+      <c r="M64" s="6" t="n"/>
+      <c r="N64" s="9" t="n"/>
+      <c r="O64" s="19" t="str">
+        <f>IF(OR($H64="",$H64=0),"",IF(COUNTIFS($A$5:$A$64,$A64,$B$5:$B$64,"&gt;"&amp;$B64)&gt;0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="P64" s="20" t="str">
+        <f>IF(AND($H64&lt;&gt;"",$H64&lt;&gt;0,NOT(OR($L64="Reforecast",$L64="Accepted"))),"YES","")</f>
+        <v/>
+      </c>
+      <c r="Q64" s="21" t="str">
+        <f>IF(OR($H64="",$H64=0),"",IF(OR($L64="Reforecast",$L64="Accepted"),"Signed off: "&amp;$L64,IF($O64="Yes","Reforecast entered — confirm sign-off","Awaiting reforecast")))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:Q64"/>
   <conditionalFormatting sqref="H5:H64">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
@@ -3426,13 +4669,26 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <conditionalFormatting sqref="P5:P64">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q64">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>AND($Q5&lt;&gt;"",LEFT($Q5,6)&lt;&gt;"Signed")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
     <dataValidation sqref="A5:A64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='Matters Register'!$A$5:$A$44</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="% complete" error="Enter cumulative % complete as a fraction between 0 and 1 (e.g. 0.25 for 25%)." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="L5:L64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Open,Reforecast,Accepted"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3564,92 +4820,92 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
-      <c r="B11" s="18" t="n"/>
+      <c r="B11" s="22" t="n"/>
       <c r="C11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
-      <c r="B12" s="18" t="n"/>
+      <c r="B12" s="22" t="n"/>
       <c r="C12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
-      <c r="B13" s="18" t="n"/>
+      <c r="B13" s="22" t="n"/>
       <c r="C13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
-      <c r="B14" s="18" t="n"/>
+      <c r="B14" s="22" t="n"/>
       <c r="C14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
-      <c r="B15" s="18" t="n"/>
+      <c r="B15" s="22" t="n"/>
       <c r="C15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
-      <c r="B16" s="18" t="n"/>
+      <c r="B16" s="22" t="n"/>
       <c r="C16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
-      <c r="B17" s="18" t="n"/>
+      <c r="B17" s="22" t="n"/>
       <c r="C17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
-      <c r="B18" s="18" t="n"/>
+      <c r="B18" s="22" t="n"/>
       <c r="C18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
-      <c r="B19" s="18" t="n"/>
+      <c r="B19" s="22" t="n"/>
       <c r="C19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
-      <c r="B20" s="18" t="n"/>
+      <c r="B20" s="22" t="n"/>
       <c r="C20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
-      <c r="B21" s="18" t="n"/>
+      <c r="B21" s="22" t="n"/>
       <c r="C21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
-      <c r="B22" s="18" t="n"/>
+      <c r="B22" s="22" t="n"/>
       <c r="C22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
-      <c r="B23" s="18" t="n"/>
+      <c r="B23" s="22" t="n"/>
       <c r="C23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="18" t="n"/>
+      <c r="B24" s="22" t="n"/>
       <c r="C24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
-      <c r="B25" s="18" t="n"/>
+      <c r="B25" s="22" t="n"/>
       <c r="C25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
-      <c r="B26" s="18" t="n"/>
+      <c r="B26" s="22" t="n"/>
       <c r="C26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
-      <c r="B27" s="18" t="n"/>
+      <c r="B27" s="22" t="n"/>
       <c r="C27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
-      <c r="B28" s="18" t="n"/>
+      <c r="B28" s="22" t="n"/>
       <c r="C28" s="8" t="n"/>
     </row>
   </sheetData>
@@ -3671,22 +4927,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="3" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3764,9 +5021,14 @@
           <t>% Recognised</t>
         </is>
       </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Open Var (#)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="23" t="n">
         <v>46266</v>
       </c>
       <c r="B5" s="17">
@@ -3781,19 +5043,19 @@
         <f>$C5-$B5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="20" t="str">
+      <c r="F5" s="24" t="str">
         <f>IF('Matters Register'!$A5="","",'Matters Register'!$A5)</f>
         <v>M-1001</v>
       </c>
-      <c r="G5" s="21" t="str">
+      <c r="G5" s="18" t="str">
         <f>IF($F5="","",'Matters Register'!$B5)</f>
         <v>Aurora Retail Group</v>
       </c>
-      <c r="H5" s="21" t="str">
+      <c r="H5" s="18" t="str">
         <f>IF($F5="","",'Matters Register'!$D5)</f>
         <v>Priya Shah</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="25">
         <f>IF($F5="","",'Matters Register'!$E5)</f>
         <v>120000</v>
       </c>
@@ -3809,13 +5071,17 @@
         <f>IF($F5="","",I5-K5)</f>
         <v>67000</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="26">
         <f>IF(OR($F5="",I5=0),"",K5/I5)</f>
         <v>0.44166666666666665</v>
       </c>
+      <c r="N5" s="27">
+        <f>IF($F5="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F5,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="23" t="n">
         <v>46296</v>
       </c>
       <c r="B6" s="17">
@@ -3830,19 +5096,19 @@
         <f>$C6-$B6</f>
         <v>-4000</v>
       </c>
-      <c r="F6" s="20" t="str">
+      <c r="F6" s="24" t="str">
         <f>IF('Matters Register'!$A6="","",'Matters Register'!$A6)</f>
         <v>M-1002</v>
       </c>
-      <c r="G6" s="21" t="str">
+      <c r="G6" s="18" t="str">
         <f>IF($F6="","",'Matters Register'!$B6)</f>
         <v>Northwind Energy</v>
       </c>
-      <c r="H6" s="21" t="str">
+      <c r="H6" s="18" t="str">
         <f>IF($F6="","",'Matters Register'!$D6)</f>
         <v>James Okoro</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="25">
         <f>IF($F6="","",'Matters Register'!$E6)</f>
         <v>90000</v>
       </c>
@@ -3858,13 +5124,17 @@
         <f>IF($F6="","",I6-K6)</f>
         <v>76500</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="26">
         <f>IF(OR($F6="",I6=0),"",K6/I6)</f>
         <v>0.15</v>
       </c>
+      <c r="N6" s="27">
+        <f>IF($F6="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F6,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="23" t="n">
         <v>46327</v>
       </c>
       <c r="B7" s="17">
@@ -3879,19 +5149,19 @@
         <f>$C7-$B7</f>
         <v>-26500</v>
       </c>
-      <c r="F7" s="20" t="str">
+      <c r="F7" s="24" t="str">
         <f>IF('Matters Register'!$A7="","",'Matters Register'!$A7)</f>
         <v>M-1003</v>
       </c>
-      <c r="G7" s="21" t="str">
+      <c r="G7" s="18" t="str">
         <f>IF($F7="","",'Matters Register'!$B7)</f>
         <v>Meridian Health</v>
       </c>
-      <c r="H7" s="21" t="str">
+      <c r="H7" s="18" t="str">
         <f>IF($F7="","",'Matters Register'!$D7)</f>
         <v>Priya Shah</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="25">
         <f>IF($F7="","",'Matters Register'!$E7)</f>
         <v>60000</v>
       </c>
@@ -3907,13 +5177,17 @@
         <f>IF($F7="","",I7-K7)</f>
         <v>37000</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="26">
         <f>IF(OR($F7="",I7=0),"",K7/I7)</f>
         <v>0.38333333333333336</v>
       </c>
+      <c r="N7" s="27">
+        <f>IF($F7="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F7,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="23" t="n">
         <v>46357</v>
       </c>
       <c r="B8" s="17">
@@ -3928,19 +5202,19 @@
         <f>$C8-$B8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="20" t="str">
+      <c r="F8" s="24" t="str">
         <f>IF('Matters Register'!$A8="","",'Matters Register'!$A8)</f>
         <v/>
       </c>
-      <c r="G8" s="21" t="str">
+      <c r="G8" s="18" t="str">
         <f>IF($F8="","",'Matters Register'!$B8)</f>
         <v/>
       </c>
-      <c r="H8" s="21" t="str">
+      <c r="H8" s="18" t="str">
         <f>IF($F8="","",'Matters Register'!$D8)</f>
         <v/>
       </c>
-      <c r="I8" s="22" t="str">
+      <c r="I8" s="25" t="str">
         <f>IF($F8="","",'Matters Register'!$E8)</f>
         <v/>
       </c>
@@ -3956,13 +5230,17 @@
         <f>IF($F8="","",I8-K8)</f>
         <v/>
       </c>
-      <c r="M8" s="23" t="str">
+      <c r="M8" s="26" t="str">
         <f>IF(OR($F8="",I8=0),"",K8/I8)</f>
         <v/>
       </c>
+      <c r="N8" s="27" t="str">
+        <f>IF($F8="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F8,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="23" t="n">
         <v>46388</v>
       </c>
       <c r="B9" s="17">
@@ -3977,19 +5255,19 @@
         <f>$C9-$B9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="20" t="str">
+      <c r="F9" s="24" t="str">
         <f>IF('Matters Register'!$A9="","",'Matters Register'!$A9)</f>
         <v/>
       </c>
-      <c r="G9" s="21" t="str">
+      <c r="G9" s="18" t="str">
         <f>IF($F9="","",'Matters Register'!$B9)</f>
         <v/>
       </c>
-      <c r="H9" s="21" t="str">
+      <c r="H9" s="18" t="str">
         <f>IF($F9="","",'Matters Register'!$D9)</f>
         <v/>
       </c>
-      <c r="I9" s="22" t="str">
+      <c r="I9" s="25" t="str">
         <f>IF($F9="","",'Matters Register'!$E9)</f>
         <v/>
       </c>
@@ -4005,13 +5283,17 @@
         <f>IF($F9="","",I9-K9)</f>
         <v/>
       </c>
-      <c r="M9" s="23" t="str">
+      <c r="M9" s="26" t="str">
         <f>IF(OR($F9="",I9=0),"",K9/I9)</f>
         <v/>
       </c>
+      <c r="N9" s="27" t="str">
+        <f>IF($F9="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F9,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="23" t="n">
         <v>46419</v>
       </c>
       <c r="B10" s="17">
@@ -4026,19 +5308,19 @@
         <f>$C10-$B10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="20" t="str">
+      <c r="F10" s="24" t="str">
         <f>IF('Matters Register'!$A10="","",'Matters Register'!$A10)</f>
         <v/>
       </c>
-      <c r="G10" s="21" t="str">
+      <c r="G10" s="18" t="str">
         <f>IF($F10="","",'Matters Register'!$B10)</f>
         <v/>
       </c>
-      <c r="H10" s="21" t="str">
+      <c r="H10" s="18" t="str">
         <f>IF($F10="","",'Matters Register'!$D10)</f>
         <v/>
       </c>
-      <c r="I10" s="22" t="str">
+      <c r="I10" s="25" t="str">
         <f>IF($F10="","",'Matters Register'!$E10)</f>
         <v/>
       </c>
@@ -4054,13 +5336,17 @@
         <f>IF($F10="","",I10-K10)</f>
         <v/>
       </c>
-      <c r="M10" s="23" t="str">
+      <c r="M10" s="26" t="str">
         <f>IF(OR($F10="",I10=0),"",K10/I10)</f>
         <v/>
       </c>
+      <c r="N10" s="27" t="str">
+        <f>IF($F10="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F10,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="23" t="n">
         <v>46447</v>
       </c>
       <c r="B11" s="17">
@@ -4075,19 +5361,19 @@
         <f>$C11-$B11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="20" t="str">
+      <c r="F11" s="24" t="str">
         <f>IF('Matters Register'!$A11="","",'Matters Register'!$A11)</f>
         <v/>
       </c>
-      <c r="G11" s="21" t="str">
+      <c r="G11" s="18" t="str">
         <f>IF($F11="","",'Matters Register'!$B11)</f>
         <v/>
       </c>
-      <c r="H11" s="21" t="str">
+      <c r="H11" s="18" t="str">
         <f>IF($F11="","",'Matters Register'!$D11)</f>
         <v/>
       </c>
-      <c r="I11" s="22" t="str">
+      <c r="I11" s="25" t="str">
         <f>IF($F11="","",'Matters Register'!$E11)</f>
         <v/>
       </c>
@@ -4103,13 +5389,17 @@
         <f>IF($F11="","",I11-K11)</f>
         <v/>
       </c>
-      <c r="M11" s="23" t="str">
+      <c r="M11" s="26" t="str">
         <f>IF(OR($F11="",I11=0),"",K11/I11)</f>
         <v/>
       </c>
+      <c r="N11" s="27" t="str">
+        <f>IF($F11="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F11,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="23" t="n">
         <v>46478</v>
       </c>
       <c r="B12" s="17">
@@ -4124,19 +5414,19 @@
         <f>$C12-$B12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="20" t="str">
+      <c r="F12" s="24" t="str">
         <f>IF('Matters Register'!$A12="","",'Matters Register'!$A12)</f>
         <v/>
       </c>
-      <c r="G12" s="21" t="str">
+      <c r="G12" s="18" t="str">
         <f>IF($F12="","",'Matters Register'!$B12)</f>
         <v/>
       </c>
-      <c r="H12" s="21" t="str">
+      <c r="H12" s="18" t="str">
         <f>IF($F12="","",'Matters Register'!$D12)</f>
         <v/>
       </c>
-      <c r="I12" s="22" t="str">
+      <c r="I12" s="25" t="str">
         <f>IF($F12="","",'Matters Register'!$E12)</f>
         <v/>
       </c>
@@ -4152,13 +5442,17 @@
         <f>IF($F12="","",I12-K12)</f>
         <v/>
       </c>
-      <c r="M12" s="23" t="str">
+      <c r="M12" s="26" t="str">
         <f>IF(OR($F12="",I12=0),"",K12/I12)</f>
         <v/>
       </c>
+      <c r="N12" s="27" t="str">
+        <f>IF($F12="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F12,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="23" t="n">
         <v>46508</v>
       </c>
       <c r="B13" s="17">
@@ -4173,19 +5467,19 @@
         <f>$C13-$B13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="20" t="str">
+      <c r="F13" s="24" t="str">
         <f>IF('Matters Register'!$A13="","",'Matters Register'!$A13)</f>
         <v/>
       </c>
-      <c r="G13" s="21" t="str">
+      <c r="G13" s="18" t="str">
         <f>IF($F13="","",'Matters Register'!$B13)</f>
         <v/>
       </c>
-      <c r="H13" s="21" t="str">
+      <c r="H13" s="18" t="str">
         <f>IF($F13="","",'Matters Register'!$D13)</f>
         <v/>
       </c>
-      <c r="I13" s="22" t="str">
+      <c r="I13" s="25" t="str">
         <f>IF($F13="","",'Matters Register'!$E13)</f>
         <v/>
       </c>
@@ -4201,13 +5495,17 @@
         <f>IF($F13="","",I13-K13)</f>
         <v/>
       </c>
-      <c r="M13" s="23" t="str">
+      <c r="M13" s="26" t="str">
         <f>IF(OR($F13="",I13=0),"",K13/I13)</f>
         <v/>
       </c>
+      <c r="N13" s="27" t="str">
+        <f>IF($F13="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F13,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="23" t="n">
         <v>46539</v>
       </c>
       <c r="B14" s="17">
@@ -4222,19 +5520,19 @@
         <f>$C14-$B14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="20" t="str">
+      <c r="F14" s="24" t="str">
         <f>IF('Matters Register'!$A14="","",'Matters Register'!$A14)</f>
         <v/>
       </c>
-      <c r="G14" s="21" t="str">
+      <c r="G14" s="18" t="str">
         <f>IF($F14="","",'Matters Register'!$B14)</f>
         <v/>
       </c>
-      <c r="H14" s="21" t="str">
+      <c r="H14" s="18" t="str">
         <f>IF($F14="","",'Matters Register'!$D14)</f>
         <v/>
       </c>
-      <c r="I14" s="22" t="str">
+      <c r="I14" s="25" t="str">
         <f>IF($F14="","",'Matters Register'!$E14)</f>
         <v/>
       </c>
@@ -4250,13 +5548,17 @@
         <f>IF($F14="","",I14-K14)</f>
         <v/>
       </c>
-      <c r="M14" s="23" t="str">
+      <c r="M14" s="26" t="str">
         <f>IF(OR($F14="",I14=0),"",K14/I14)</f>
         <v/>
       </c>
+      <c r="N14" s="27" t="str">
+        <f>IF($F14="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F14,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="23" t="n">
         <v>46569</v>
       </c>
       <c r="B15" s="17">
@@ -4271,19 +5573,19 @@
         <f>$C15-$B15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="20" t="str">
+      <c r="F15" s="24" t="str">
         <f>IF('Matters Register'!$A15="","",'Matters Register'!$A15)</f>
         <v/>
       </c>
-      <c r="G15" s="21" t="str">
+      <c r="G15" s="18" t="str">
         <f>IF($F15="","",'Matters Register'!$B15)</f>
         <v/>
       </c>
-      <c r="H15" s="21" t="str">
+      <c r="H15" s="18" t="str">
         <f>IF($F15="","",'Matters Register'!$D15)</f>
         <v/>
       </c>
-      <c r="I15" s="22" t="str">
+      <c r="I15" s="25" t="str">
         <f>IF($F15="","",'Matters Register'!$E15)</f>
         <v/>
       </c>
@@ -4299,13 +5601,17 @@
         <f>IF($F15="","",I15-K15)</f>
         <v/>
       </c>
-      <c r="M15" s="23" t="str">
+      <c r="M15" s="26" t="str">
         <f>IF(OR($F15="",I15=0),"",K15/I15)</f>
         <v/>
       </c>
+      <c r="N15" s="27" t="str">
+        <f>IF($F15="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F15,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="n">
+      <c r="A16" s="23" t="n">
         <v>46600</v>
       </c>
       <c r="B16" s="17">
@@ -4320,19 +5626,19 @@
         <f>$C16-$B16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="20" t="str">
+      <c r="F16" s="24" t="str">
         <f>IF('Matters Register'!$A16="","",'Matters Register'!$A16)</f>
         <v/>
       </c>
-      <c r="G16" s="21" t="str">
+      <c r="G16" s="18" t="str">
         <f>IF($F16="","",'Matters Register'!$B16)</f>
         <v/>
       </c>
-      <c r="H16" s="21" t="str">
+      <c r="H16" s="18" t="str">
         <f>IF($F16="","",'Matters Register'!$D16)</f>
         <v/>
       </c>
-      <c r="I16" s="22" t="str">
+      <c r="I16" s="25" t="str">
         <f>IF($F16="","",'Matters Register'!$E16)</f>
         <v/>
       </c>
@@ -4348,42 +5654,46 @@
         <f>IF($F16="","",I16-K16)</f>
         <v/>
       </c>
-      <c r="M16" s="23" t="str">
+      <c r="M16" s="26" t="str">
         <f>IF(OR($F16="",I16=0),"",K16/I16)</f>
         <v/>
       </c>
+      <c r="N16" s="27" t="str">
+        <f>IF($F16="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F16,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="29">
         <f>SUM(B5:B16)</f>
         <v>120000</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="29">
         <f>SUM(C5:C16)</f>
         <v>89500</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="29">
         <f>SUM(D5:D16)</f>
         <v>-30500</v>
       </c>
-      <c r="F17" s="20" t="str">
+      <c r="F17" s="24" t="str">
         <f>IF('Matters Register'!$A17="","",'Matters Register'!$A17)</f>
         <v/>
       </c>
-      <c r="G17" s="21" t="str">
+      <c r="G17" s="18" t="str">
         <f>IF($F17="","",'Matters Register'!$B17)</f>
         <v/>
       </c>
-      <c r="H17" s="21" t="str">
+      <c r="H17" s="18" t="str">
         <f>IF($F17="","",'Matters Register'!$D17)</f>
         <v/>
       </c>
-      <c r="I17" s="22" t="str">
+      <c r="I17" s="25" t="str">
         <f>IF($F17="","",'Matters Register'!$E17)</f>
         <v/>
       </c>
@@ -4399,25 +5709,29 @@
         <f>IF($F17="","",I17-K17)</f>
         <v/>
       </c>
-      <c r="M17" s="23" t="str">
+      <c r="M17" s="26" t="str">
         <f>IF(OR($F17="",I17=0),"",K17/I17)</f>
         <v/>
       </c>
+      <c r="N17" s="27" t="str">
+        <f>IF($F17="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F17,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="F18" s="20" t="str">
+      <c r="F18" s="24" t="str">
         <f>IF('Matters Register'!$A18="","",'Matters Register'!$A18)</f>
         <v/>
       </c>
-      <c r="G18" s="21" t="str">
+      <c r="G18" s="18" t="str">
         <f>IF($F18="","",'Matters Register'!$B18)</f>
         <v/>
       </c>
-      <c r="H18" s="21" t="str">
+      <c r="H18" s="18" t="str">
         <f>IF($F18="","",'Matters Register'!$D18)</f>
         <v/>
       </c>
-      <c r="I18" s="22" t="str">
+      <c r="I18" s="25" t="str">
         <f>IF($F18="","",'Matters Register'!$E18)</f>
         <v/>
       </c>
@@ -4433,25 +5747,34 @@
         <f>IF($F18="","",I18-K18)</f>
         <v/>
       </c>
-      <c r="M18" s="23" t="str">
+      <c r="M18" s="26" t="str">
         <f>IF(OR($F18="",I18=0),"",K18/I18)</f>
         <v/>
       </c>
+      <c r="N18" s="27" t="str">
+        <f>IF($F18="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F18,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="F19" s="20" t="str">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>Open Variances — flagged but not yet reforecast</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="str">
         <f>IF('Matters Register'!$A19="","",'Matters Register'!$A19)</f>
         <v/>
       </c>
-      <c r="G19" s="21" t="str">
+      <c r="G19" s="18" t="str">
         <f>IF($F19="","",'Matters Register'!$B19)</f>
         <v/>
       </c>
-      <c r="H19" s="21" t="str">
+      <c r="H19" s="18" t="str">
         <f>IF($F19="","",'Matters Register'!$D19)</f>
         <v/>
       </c>
-      <c r="I19" s="22" t="str">
+      <c r="I19" s="25" t="str">
         <f>IF($F19="","",'Matters Register'!$E19)</f>
         <v/>
       </c>
@@ -4467,25 +5790,38 @@
         <f>IF($F19="","",I19-K19)</f>
         <v/>
       </c>
-      <c r="M19" s="23" t="str">
+      <c r="M19" s="26" t="str">
         <f>IF(OR($F19="",I19=0),"",K19/I19)</f>
         <v/>
       </c>
+      <c r="N19" s="27" t="str">
+        <f>IF($F19="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F19,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="F20" s="20" t="str">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>Open items (#)</t>
+        </is>
+      </c>
+      <c r="B20" s="32">
+        <f>COUNTIF('Forecast Log'!$P$5:$P$64,"YES")</f>
+        <v>2</v>
+      </c>
+      <c r="F20" s="24" t="str">
         <f>IF('Matters Register'!$A20="","",'Matters Register'!$A20)</f>
         <v/>
       </c>
-      <c r="G20" s="21" t="str">
+      <c r="G20" s="18" t="str">
         <f>IF($F20="","",'Matters Register'!$B20)</f>
         <v/>
       </c>
-      <c r="H20" s="21" t="str">
+      <c r="H20" s="18" t="str">
         <f>IF($F20="","",'Matters Register'!$D20)</f>
         <v/>
       </c>
-      <c r="I20" s="22" t="str">
+      <c r="I20" s="25" t="str">
         <f>IF($F20="","",'Matters Register'!$E20)</f>
         <v/>
       </c>
@@ -4501,25 +5837,38 @@
         <f>IF($F20="","",I20-K20)</f>
         <v/>
       </c>
-      <c r="M20" s="23" t="str">
+      <c r="M20" s="26" t="str">
         <f>IF(OR($F20="",I20=0),"",K20/I20)</f>
         <v/>
       </c>
+      <c r="N20" s="27" t="str">
+        <f>IF($F20="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F20,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="F21" s="20" t="str">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>Open value (£, net)</t>
+        </is>
+      </c>
+      <c r="B21" s="33">
+        <f>SUMIFS('Forecast Log'!$H$5:$H$64,'Forecast Log'!$P$5:$P$64,"YES")</f>
+        <v>-1000</v>
+      </c>
+      <c r="F21" s="24" t="str">
         <f>IF('Matters Register'!$A21="","",'Matters Register'!$A21)</f>
         <v/>
       </c>
-      <c r="G21" s="21" t="str">
+      <c r="G21" s="18" t="str">
         <f>IF($F21="","",'Matters Register'!$B21)</f>
         <v/>
       </c>
-      <c r="H21" s="21" t="str">
+      <c r="H21" s="18" t="str">
         <f>IF($F21="","",'Matters Register'!$D21)</f>
         <v/>
       </c>
-      <c r="I21" s="22" t="str">
+      <c r="I21" s="25" t="str">
         <f>IF($F21="","",'Matters Register'!$E21)</f>
         <v/>
       </c>
@@ -4535,25 +5884,38 @@
         <f>IF($F21="","",I21-K21)</f>
         <v/>
       </c>
-      <c r="M21" s="23" t="str">
+      <c r="M21" s="26" t="str">
         <f>IF(OR($F21="",I21=0),"",K21/I21)</f>
         <v/>
       </c>
+      <c r="N21" s="27" t="str">
+        <f>IF($F21="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F21,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="F22" s="20" t="str">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>Oldest open month</t>
+        </is>
+      </c>
+      <c r="B22" s="34">
+        <f>IF(COUNTIF('Forecast Log'!$P$5:$P$64,"YES")=0,"",_xlfn.MINIFS('Forecast Log'!$B$5:$B$64,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v>46296</v>
+      </c>
+      <c r="F22" s="24" t="str">
         <f>IF('Matters Register'!$A22="","",'Matters Register'!$A22)</f>
         <v/>
       </c>
-      <c r="G22" s="21" t="str">
+      <c r="G22" s="18" t="str">
         <f>IF($F22="","",'Matters Register'!$B22)</f>
         <v/>
       </c>
-      <c r="H22" s="21" t="str">
+      <c r="H22" s="18" t="str">
         <f>IF($F22="","",'Matters Register'!$D22)</f>
         <v/>
       </c>
-      <c r="I22" s="22" t="str">
+      <c r="I22" s="25" t="str">
         <f>IF($F22="","",'Matters Register'!$E22)</f>
         <v/>
       </c>
@@ -4569,25 +5931,29 @@
         <f>IF($F22="","",I22-K22)</f>
         <v/>
       </c>
-      <c r="M22" s="23" t="str">
+      <c r="M22" s="26" t="str">
         <f>IF(OR($F22="",I22=0),"",K22/I22)</f>
         <v/>
       </c>
+      <c r="N22" s="27" t="str">
+        <f>IF($F22="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F22,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="F23" s="20" t="str">
+      <c r="F23" s="24" t="str">
         <f>IF('Matters Register'!$A23="","",'Matters Register'!$A23)</f>
         <v/>
       </c>
-      <c r="G23" s="21" t="str">
+      <c r="G23" s="18" t="str">
         <f>IF($F23="","",'Matters Register'!$B23)</f>
         <v/>
       </c>
-      <c r="H23" s="21" t="str">
+      <c r="H23" s="18" t="str">
         <f>IF($F23="","",'Matters Register'!$D23)</f>
         <v/>
       </c>
-      <c r="I23" s="22" t="str">
+      <c r="I23" s="25" t="str">
         <f>IF($F23="","",'Matters Register'!$E23)</f>
         <v/>
       </c>
@@ -4603,25 +5969,29 @@
         <f>IF($F23="","",I23-K23)</f>
         <v/>
       </c>
-      <c r="M23" s="23" t="str">
+      <c r="M23" s="26" t="str">
         <f>IF(OR($F23="",I23=0),"",K23/I23)</f>
         <v/>
       </c>
+      <c r="N23" s="27" t="str">
+        <f>IF($F23="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F23,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="F24" s="20" t="str">
+      <c r="F24" s="24" t="str">
         <f>IF('Matters Register'!$A24="","",'Matters Register'!$A24)</f>
         <v/>
       </c>
-      <c r="G24" s="21" t="str">
+      <c r="G24" s="18" t="str">
         <f>IF($F24="","",'Matters Register'!$B24)</f>
         <v/>
       </c>
-      <c r="H24" s="21" t="str">
+      <c r="H24" s="18" t="str">
         <f>IF($F24="","",'Matters Register'!$D24)</f>
         <v/>
       </c>
-      <c r="I24" s="22" t="str">
+      <c r="I24" s="25" t="str">
         <f>IF($F24="","",'Matters Register'!$E24)</f>
         <v/>
       </c>
@@ -4637,8 +6007,12 @@
         <f>IF($F24="","",I24-K24)</f>
         <v/>
       </c>
-      <c r="M24" s="23" t="str">
+      <c r="M24" s="26" t="str">
         <f>IF(OR($F24="",I24=0),"",K24/I24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="27" t="str">
+        <f>IF($F24="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F24,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
     </row>
@@ -4663,6 +6037,11 @@
       <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Actual to Date (£)</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Open (#)</t>
         </is>
       </c>
     </row>
@@ -4680,6 +6059,10 @@
         <f>SUMIF($H$5:$H$24,$F28,$K$5:$K$24)</f>
         <v>76000</v>
       </c>
+      <c r="I28" s="27">
+        <f>COUNTIFS('Forecast Log'!$K$5:$K$64,$F28,'Forecast Log'!$P$5:$P$64,"YES")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="F29" s="7" t="inlineStr">
@@ -4694,6 +6077,10 @@
       <c r="H29" s="17">
         <f>SUMIF($H$5:$H$24,$F29,$K$5:$K$24)</f>
         <v>13500</v>
+      </c>
+      <c r="I29" s="27">
+        <f>COUNTIFS('Forecast Log'!$K$5:$K$64,$F29,'Forecast Log'!$P$5:$P$64,"YES")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4705,6 +6092,21 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N5:N24">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28:I29">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
